--- a/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65240_completo.xlsx
+++ b/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65240_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra8994d1b16104c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8070d4d251c64be9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,546 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65240_completo.xlsx
+++ b/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65240_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8070d4d251c64be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4781dcec3b09419d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2826 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.7800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.8900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
